--- a/POLES.xlsx
+++ b/POLES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Repositories\Section Drawing Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19CA9555-9935-45A4-9E90-306688EEDAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F959484C-EB40-4B85-8D59-7CC9BF103CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{A08279BC-EBA8-43EC-B245-051A369EF083}"/>
+    <workbookView xWindow="-2460" yWindow="3820" windowWidth="19200" windowHeight="11170" xr2:uid="{A08279BC-EBA8-43EC-B245-051A369EF083}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>pole_number</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>TYPE1</t>
+  </si>
+  <si>
+    <t>TYPE2</t>
+  </si>
+  <si>
+    <t>TYPE3</t>
   </si>
 </sst>
 </file>
@@ -117,10 +123,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,8 +444,8 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="4" customWidth="1"/>
-    <col min="2" max="4" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="12.08984375" style="3" customWidth="1"/>
+    <col min="2" max="4" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
@@ -461,12 +467,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>164548.46100000001</v>
+        <v>167326.962</v>
       </c>
       <c r="C2" s="2">
-        <v>581610.50199999998</v>
-      </c>
-      <c r="D2" s="3" t="s">
+        <v>580464.96100000001</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -475,13 +481,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>164554.80600000001</v>
+        <v>167329.071</v>
       </c>
       <c r="C3" s="2">
-        <v>581621.28700000001</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>580476.54799999995</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -489,12 +495,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>164600.12899999999</v>
+        <v>167379.93</v>
       </c>
       <c r="C4" s="2">
-        <v>581579.93200000003</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>580454.60699999996</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -503,13 +509,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>164606.50399999999</v>
+        <v>167381.954</v>
       </c>
       <c r="C5" s="2">
-        <v>581590.44999999995</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>580465.902</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -517,13 +523,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>164645.079</v>
+        <v>167437.78899999999</v>
       </c>
       <c r="C6" s="2">
-        <v>581552.97699999996</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>4</v>
+        <v>580443.97199999995</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -531,12 +537,12 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>164651.641</v>
+        <v>167439.88699999999</v>
       </c>
       <c r="C7" s="2">
-        <v>581563.99399999995</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>580455.43200000003</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
